--- a/declara.xlsx
+++ b/declara.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2731" uniqueCount="1320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3019" uniqueCount="1439">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -3974,6 +3974,363 @@
   </si>
   <si>
     <t>Gloria peña</t>
+  </si>
+  <si>
+    <t>lucholoza641991@gmail.com</t>
+  </si>
+  <si>
+    <t>Luciano cesar loza</t>
+  </si>
+  <si>
+    <t>Malvinas argentina 490</t>
+  </si>
+  <si>
+    <t>cementerio</t>
+  </si>
+  <si>
+    <t>Luciano loza</t>
+  </si>
+  <si>
+    <t>brianzeballez019@gmail.com</t>
+  </si>
+  <si>
+    <t>Zeballez Brian Jesus</t>
+  </si>
+  <si>
+    <t>General López 680</t>
+  </si>
+  <si>
+    <t>Recolector de residuos</t>
+  </si>
+  <si>
+    <t>Brian Jesús Zeballez</t>
+  </si>
+  <si>
+    <t>Brian Zeballez</t>
+  </si>
+  <si>
+    <t>Brian Jesús zeballez</t>
+  </si>
+  <si>
+    <t>luis0338215680291rodriguez@gmail.com</t>
+  </si>
+  <si>
+    <t>Hector luis Rodriguez</t>
+  </si>
+  <si>
+    <t>Jose moran 775</t>
+  </si>
+  <si>
+    <t>Predio</t>
+  </si>
+  <si>
+    <t>Natalia judith malano</t>
+  </si>
+  <si>
+    <t>Milagros Rodríguez</t>
+  </si>
+  <si>
+    <t>Rodriguez ludmila</t>
+  </si>
+  <si>
+    <t>Alexis Rodriguez</t>
+  </si>
+  <si>
+    <t>Rodriguez alexis</t>
+  </si>
+  <si>
+    <t>Rodriguez milagros</t>
+  </si>
+  <si>
+    <t>alcarazestrellaceleste@gmail.com</t>
+  </si>
+  <si>
+    <t>Alcaraz estrella celeste</t>
+  </si>
+  <si>
+    <t>Malvinas argentinas 866</t>
+  </si>
+  <si>
+    <t>Alcaraz Rodrigo jesus</t>
+  </si>
+  <si>
+    <t>Darío Daniel isla</t>
+  </si>
+  <si>
+    <t>Gastón Ariel Alcaraz</t>
+  </si>
+  <si>
+    <t>Estrella celeste Alcaraz</t>
+  </si>
+  <si>
+    <t>renzoa659@gmail.com</t>
+  </si>
+  <si>
+    <t>Alvarez Renzo Javier</t>
+  </si>
+  <si>
+    <t>1 de mayo 615</t>
+  </si>
+  <si>
+    <t>Rufino Santa fe</t>
+  </si>
+  <si>
+    <t>Vienes y servicio a la comunidad</t>
+  </si>
+  <si>
+    <t>Administrativo box</t>
+  </si>
+  <si>
+    <t>Oficina de cementerio</t>
+  </si>
+  <si>
+    <t>Delfina Francesca Alvarez</t>
+  </si>
+  <si>
+    <t>Patricia Griselda Carrizo</t>
+  </si>
+  <si>
+    <t>Tomas Ariel Alvarez</t>
+  </si>
+  <si>
+    <t>mirianmecchi12@gmail.com</t>
+  </si>
+  <si>
+    <t>Mecchi Miriam</t>
+  </si>
+  <si>
+    <t>_</t>
+  </si>
+  <si>
+    <t>Columna lumbar</t>
+  </si>
+  <si>
+    <t>Plaza barrio civeli</t>
+  </si>
+  <si>
+    <t>Vicente Rodolfo bracco</t>
+  </si>
+  <si>
+    <t>Bracco Daiana paola</t>
+  </si>
+  <si>
+    <t>Bracco Vicente rodolfo</t>
+  </si>
+  <si>
+    <t>fpaez8076@gmail.com</t>
+  </si>
+  <si>
+    <t>Paez Fabiana</t>
+  </si>
+  <si>
+    <t>Gral Lopez 450</t>
+  </si>
+  <si>
+    <t>3382_679795</t>
+  </si>
+  <si>
+    <t>Bazan Paez Adriana</t>
+  </si>
+  <si>
+    <t>Lic.en criminoligia y seguridad</t>
+  </si>
+  <si>
+    <t>Vidal Enzo</t>
+  </si>
+  <si>
+    <t>Adriana Bazan Paez</t>
+  </si>
+  <si>
+    <t>43.843.295</t>
+  </si>
+  <si>
+    <t>ayalasunana1983@gmail.com</t>
+  </si>
+  <si>
+    <t>Ayala Susana beatriz</t>
+  </si>
+  <si>
+    <t>Zolezzi 1280</t>
+  </si>
+  <si>
+    <t>Cursando computación</t>
+  </si>
+  <si>
+    <t>Punto digital terminal</t>
+  </si>
+  <si>
+    <t>Atención al público y limpieza</t>
+  </si>
+  <si>
+    <t>Medina candela soledad</t>
+  </si>
+  <si>
+    <t>Terciario cursando contabilidad</t>
+  </si>
+  <si>
+    <t>Emiliano Ezequiel Medina</t>
+  </si>
+  <si>
+    <t>Susana beatriz Ayala</t>
+  </si>
+  <si>
+    <t>Candela soledad Medina</t>
+  </si>
+  <si>
+    <t>pereyrakeyla08@gmail.com</t>
+  </si>
+  <si>
+    <t>Marcela Wilson</t>
+  </si>
+  <si>
+    <t>10.07.1977</t>
+  </si>
+  <si>
+    <t>Catamarca 335</t>
+  </si>
+  <si>
+    <t>Municipal</t>
+  </si>
+  <si>
+    <t>Alejandro pereyra</t>
+  </si>
+  <si>
+    <t>Fernando pereyra</t>
+  </si>
+  <si>
+    <t>Luciano Pereyra</t>
+  </si>
+  <si>
+    <t>Keyla pereyra</t>
+  </si>
+  <si>
+    <t>Luciano pereyra</t>
+  </si>
+  <si>
+    <t>mariisabelcabre@gmail.com</t>
+  </si>
+  <si>
+    <t>Isabel maria cabrera</t>
+  </si>
+  <si>
+    <t>08.07.1976</t>
+  </si>
+  <si>
+    <t>General paz 558rufíno</t>
+  </si>
+  <si>
+    <t>Quintana valentina ailen</t>
+  </si>
+  <si>
+    <t>Adrian orlando obregon</t>
+  </si>
+  <si>
+    <t>Diseñador de exteriores</t>
+  </si>
+  <si>
+    <t>betianafranco545@gmail.com</t>
+  </si>
+  <si>
+    <t>Franco Claudia Betiana</t>
+  </si>
+  <si>
+    <t>Bolivar 395</t>
+  </si>
+  <si>
+    <t>Docente del nivel inicial</t>
+  </si>
+  <si>
+    <t>Caf</t>
+  </si>
+  <si>
+    <t>Tulentinati fernando</t>
+  </si>
+  <si>
+    <t>Azcurra franco Alfonsina</t>
+  </si>
+  <si>
+    <t>Tulentinati franco catalina</t>
+  </si>
+  <si>
+    <t>Tulentinati franco Aron</t>
+  </si>
+  <si>
+    <t>cokielena654@gmail.com</t>
+  </si>
+  <si>
+    <t>Pereyra Jorgelina elena</t>
+  </si>
+  <si>
+    <t>Antonio Martín 965</t>
+  </si>
+  <si>
+    <t>3382_454353</t>
+  </si>
+  <si>
+    <t>Retamozo Santiago</t>
+  </si>
+  <si>
+    <t>Moreno Camila</t>
+  </si>
+  <si>
+    <t>Moreno Brian</t>
+  </si>
+  <si>
+    <t>Moreno mateo</t>
+  </si>
+  <si>
+    <t>Mateo moreno</t>
+  </si>
+  <si>
+    <t>retamozosantiago268@gmail.com</t>
+  </si>
+  <si>
+    <t>retamozo santiago</t>
+  </si>
+  <si>
+    <t>12_01_74</t>
+  </si>
+  <si>
+    <t>antonio martin 965</t>
+  </si>
+  <si>
+    <t>rufino santa fe</t>
+  </si>
+  <si>
+    <t>3382_444551</t>
+  </si>
+  <si>
+    <t>corralon municipal</t>
+  </si>
+  <si>
+    <t>recoleccion de residuos</t>
+  </si>
+  <si>
+    <t>pereyra jorgelina</t>
+  </si>
+  <si>
+    <t>retamozo kevin</t>
+  </si>
+  <si>
+    <t>bessonelucia.55@gmail.com</t>
+  </si>
+  <si>
+    <t>Bessone Lucia</t>
+  </si>
+  <si>
+    <t>Chacabuco 598</t>
+  </si>
+  <si>
+    <t>Curso de Excel</t>
+  </si>
+  <si>
+    <t>Ayudante de cosina, atención al ciudadano ext.</t>
+  </si>
+  <si>
+    <t>Lucas Clavero</t>
+  </si>
+  <si>
+    <t>Juliana Clavero</t>
   </si>
 </sst>
 </file>
@@ -4859,7 +5216,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY138"/>
+  <dimension ref="A1:AY152"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
@@ -21011,6 +21368,1716 @@
         <v>527</v>
       </c>
     </row>
+    <row r="139" spans="1:47" ht="39" thickBot="1">
+      <c r="A139" s="45">
+        <v>46276.519259259258</v>
+      </c>
+      <c r="B139" s="46" t="s">
+        <v>1320</v>
+      </c>
+      <c r="C139" s="46" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D139" s="47">
+        <v>34172696</v>
+      </c>
+      <c r="E139" s="48">
+        <v>33334</v>
+      </c>
+      <c r="F139" s="46" t="s">
+        <v>1322</v>
+      </c>
+      <c r="G139" s="46" t="s">
+        <v>632</v>
+      </c>
+      <c r="H139" s="47">
+        <v>3382482943</v>
+      </c>
+      <c r="I139" s="46" t="s">
+        <v>58</v>
+      </c>
+      <c r="J139" s="46" t="s">
+        <v>718</v>
+      </c>
+      <c r="K139" s="46" t="s">
+        <v>230</v>
+      </c>
+      <c r="L139" s="46" t="s">
+        <v>784</v>
+      </c>
+      <c r="M139" s="46" t="s">
+        <v>1323</v>
+      </c>
+      <c r="N139" s="46" t="s">
+        <v>1213</v>
+      </c>
+      <c r="O139" s="50">
+        <v>45505</v>
+      </c>
+      <c r="P139" s="47">
+        <v>48</v>
+      </c>
+      <c r="Q139" s="46" t="s">
+        <v>492</v>
+      </c>
+      <c r="R139" s="47">
+        <v>48</v>
+      </c>
+      <c r="S139" s="47">
+        <v>41</v>
+      </c>
+      <c r="T139" s="46" t="s">
+        <v>1321</v>
+      </c>
+      <c r="U139" s="50">
+        <v>33334</v>
+      </c>
+      <c r="V139" s="47">
+        <v>34172696</v>
+      </c>
+      <c r="W139" s="46" t="s">
+        <v>1324</v>
+      </c>
+      <c r="X139" s="50">
+        <v>33334</v>
+      </c>
+      <c r="Y139" s="47">
+        <v>34172696</v>
+      </c>
+      <c r="Z139" s="46" t="s">
+        <v>230</v>
+      </c>
+      <c r="AA139" s="46" t="s">
+        <v>230</v>
+      </c>
+      <c r="AB139" s="46" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC139" s="46" t="s">
+        <v>1324</v>
+      </c>
+      <c r="AD139" s="50">
+        <v>33334</v>
+      </c>
+      <c r="AE139" s="47">
+        <v>34172696</v>
+      </c>
+      <c r="AF139" s="46" t="s">
+        <v>230</v>
+      </c>
+      <c r="AG139" s="46" t="s">
+        <v>230</v>
+      </c>
+      <c r="AH139" s="49"/>
+      <c r="AI139" s="49"/>
+      <c r="AJ139" s="49"/>
+      <c r="AK139" s="49"/>
+      <c r="AL139" s="49"/>
+      <c r="AM139" s="49"/>
+      <c r="AN139" s="49"/>
+      <c r="AO139" s="46" t="s">
+        <v>1324</v>
+      </c>
+      <c r="AP139" s="47">
+        <v>34172696</v>
+      </c>
+      <c r="AQ139" s="46" t="s">
+        <v>1324</v>
+      </c>
+      <c r="AR139" s="47">
+        <v>34172696</v>
+      </c>
+      <c r="AS139" s="46" t="s">
+        <v>1324</v>
+      </c>
+      <c r="AT139" s="47">
+        <v>34172696</v>
+      </c>
+      <c r="AU139" s="51">
+        <v>572</v>
+      </c>
+    </row>
+    <row r="140" spans="1:47" ht="26.25" thickBot="1">
+      <c r="A140" s="6">
+        <v>46276.523923611108</v>
+      </c>
+      <c r="B140" s="7" t="s">
+        <v>1325</v>
+      </c>
+      <c r="C140" s="7" t="s">
+        <v>1326</v>
+      </c>
+      <c r="D140" s="8">
+        <v>40121253</v>
+      </c>
+      <c r="E140" s="9">
+        <v>35524</v>
+      </c>
+      <c r="F140" s="7" t="s">
+        <v>1327</v>
+      </c>
+      <c r="G140" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H140" s="8">
+        <v>3382506906</v>
+      </c>
+      <c r="I140" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J140" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K140" s="11"/>
+      <c r="L140" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M140" s="7" t="s">
+        <v>257</v>
+      </c>
+      <c r="N140" s="7" t="s">
+        <v>1328</v>
+      </c>
+      <c r="O140" s="10">
+        <v>42776</v>
+      </c>
+      <c r="P140" s="8">
+        <v>48</v>
+      </c>
+      <c r="Q140" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="R140" s="8">
+        <v>48</v>
+      </c>
+      <c r="S140" s="8">
+        <v>42</v>
+      </c>
+      <c r="T140" s="7" t="s">
+        <v>1329</v>
+      </c>
+      <c r="U140" s="10">
+        <v>35524</v>
+      </c>
+      <c r="V140" s="8">
+        <v>40121253</v>
+      </c>
+      <c r="W140" s="7" t="s">
+        <v>1326</v>
+      </c>
+      <c r="X140" s="10">
+        <v>35524</v>
+      </c>
+      <c r="Y140" s="8">
+        <v>40121253</v>
+      </c>
+      <c r="Z140" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA140" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AB140" s="11"/>
+      <c r="AC140" s="7" t="s">
+        <v>1329</v>
+      </c>
+      <c r="AD140" s="10">
+        <v>35524</v>
+      </c>
+      <c r="AE140" s="8">
+        <v>40121253</v>
+      </c>
+      <c r="AF140" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG140" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AH140" s="11"/>
+      <c r="AI140" s="7" t="s">
+        <v>1330</v>
+      </c>
+      <c r="AJ140" s="10">
+        <v>35524</v>
+      </c>
+      <c r="AK140" s="8">
+        <v>40121253</v>
+      </c>
+      <c r="AL140" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM140" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AN140" s="11"/>
+      <c r="AO140" s="7" t="s">
+        <v>1331</v>
+      </c>
+      <c r="AP140" s="8">
+        <v>40121253</v>
+      </c>
+      <c r="AQ140" s="7" t="s">
+        <v>1331</v>
+      </c>
+      <c r="AR140" s="8">
+        <v>40121253</v>
+      </c>
+      <c r="AS140" s="7" t="s">
+        <v>1329</v>
+      </c>
+      <c r="AT140" s="8">
+        <v>40121253</v>
+      </c>
+      <c r="AU140" s="28">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="141" spans="1:47" ht="39" thickBot="1">
+      <c r="A141" s="21">
+        <v>46276.604178240741</v>
+      </c>
+      <c r="B141" s="22" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C141" s="22" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D141" s="23">
+        <v>32348113</v>
+      </c>
+      <c r="E141" s="24">
+        <v>31622</v>
+      </c>
+      <c r="F141" s="22" t="s">
+        <v>1334</v>
+      </c>
+      <c r="G141" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H141" s="23">
+        <v>672475</v>
+      </c>
+      <c r="I141" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="J141" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="K141" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="L141" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="M141" s="22" t="s">
+        <v>1335</v>
+      </c>
+      <c r="N141" s="22" t="s">
+        <v>316</v>
+      </c>
+      <c r="O141" s="25">
+        <v>43282</v>
+      </c>
+      <c r="P141" s="23">
+        <v>44</v>
+      </c>
+      <c r="Q141" s="23">
+        <v>5</v>
+      </c>
+      <c r="R141" s="23">
+        <v>44</v>
+      </c>
+      <c r="S141" s="23">
+        <v>41</v>
+      </c>
+      <c r="T141" s="22" t="s">
+        <v>1336</v>
+      </c>
+      <c r="U141" s="25">
+        <v>33990</v>
+      </c>
+      <c r="V141" s="23">
+        <v>38250015</v>
+      </c>
+      <c r="W141" s="22" t="s">
+        <v>1337</v>
+      </c>
+      <c r="X141" s="25">
+        <v>39903</v>
+      </c>
+      <c r="Y141" s="23">
+        <v>49267985</v>
+      </c>
+      <c r="Z141" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA141" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB141" s="26"/>
+      <c r="AC141" s="22" t="s">
+        <v>1338</v>
+      </c>
+      <c r="AD141" s="25">
+        <v>40549</v>
+      </c>
+      <c r="AE141" s="23">
+        <v>50642537</v>
+      </c>
+      <c r="AF141" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG141" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH141" s="26"/>
+      <c r="AI141" s="22" t="s">
+        <v>1339</v>
+      </c>
+      <c r="AJ141" s="25">
+        <v>41100</v>
+      </c>
+      <c r="AK141" s="23">
+        <v>52363290</v>
+      </c>
+      <c r="AL141" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM141" s="26"/>
+      <c r="AN141" s="26"/>
+      <c r="AO141" s="22" t="s">
+        <v>1340</v>
+      </c>
+      <c r="AP141" s="23">
+        <v>52363290</v>
+      </c>
+      <c r="AQ141" s="22" t="s">
+        <v>1341</v>
+      </c>
+      <c r="AR141" s="23">
+        <v>49267985</v>
+      </c>
+      <c r="AS141" s="22" t="s">
+        <v>1338</v>
+      </c>
+      <c r="AT141" s="23">
+        <v>50642537</v>
+      </c>
+      <c r="AU141" s="27">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="142" spans="1:47" ht="39" thickBot="1">
+      <c r="A142" s="6">
+        <v>46276.645682870374</v>
+      </c>
+      <c r="B142" s="7" t="s">
+        <v>1342</v>
+      </c>
+      <c r="C142" s="7" t="s">
+        <v>1343</v>
+      </c>
+      <c r="D142" s="8">
+        <v>31225509</v>
+      </c>
+      <c r="E142" s="9">
+        <v>30863</v>
+      </c>
+      <c r="F142" s="7" t="s">
+        <v>1344</v>
+      </c>
+      <c r="G142" s="7" t="s">
+        <v>957</v>
+      </c>
+      <c r="H142" s="8">
+        <v>3382390825</v>
+      </c>
+      <c r="I142" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J142" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K142" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="L142" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="M142" s="7" t="s">
+        <v>790</v>
+      </c>
+      <c r="N142" s="7" t="s">
+        <v>719</v>
+      </c>
+      <c r="O142" s="10">
+        <v>44896</v>
+      </c>
+      <c r="P142" s="8">
+        <v>58</v>
+      </c>
+      <c r="Q142" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="R142" s="8">
+        <v>58</v>
+      </c>
+      <c r="S142" s="8">
+        <v>40</v>
+      </c>
+      <c r="T142" s="11"/>
+      <c r="U142" s="10">
+        <v>30863</v>
+      </c>
+      <c r="V142" s="11"/>
+      <c r="W142" s="7" t="s">
+        <v>1345</v>
+      </c>
+      <c r="X142" s="10">
+        <v>36912</v>
+      </c>
+      <c r="Y142" s="8">
+        <v>43647723</v>
+      </c>
+      <c r="Z142" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA142" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AB142" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC142" s="7" t="s">
+        <v>1346</v>
+      </c>
+      <c r="AD142" s="10">
+        <v>37792</v>
+      </c>
+      <c r="AE142" s="8">
+        <v>44996078</v>
+      </c>
+      <c r="AF142" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG142" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AH142" s="11"/>
+      <c r="AI142" s="7" t="s">
+        <v>1347</v>
+      </c>
+      <c r="AJ142" s="10">
+        <v>39840</v>
+      </c>
+      <c r="AK142" s="8">
+        <v>49060366</v>
+      </c>
+      <c r="AL142" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM142" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AN142" s="11"/>
+      <c r="AO142" s="7" t="s">
+        <v>1348</v>
+      </c>
+      <c r="AP142" s="8">
+        <v>31225509</v>
+      </c>
+      <c r="AQ142" s="7" t="s">
+        <v>1348</v>
+      </c>
+      <c r="AR142" s="8">
+        <v>31225509</v>
+      </c>
+      <c r="AS142" s="7" t="s">
+        <v>1348</v>
+      </c>
+      <c r="AT142" s="8">
+        <v>31225509</v>
+      </c>
+      <c r="AU142" s="28">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="143" spans="1:47" ht="39" thickBot="1">
+      <c r="A143" s="21">
+        <v>46276.80672453704</v>
+      </c>
+      <c r="B143" s="22" t="s">
+        <v>1349</v>
+      </c>
+      <c r="C143" s="22" t="s">
+        <v>1350</v>
+      </c>
+      <c r="D143" s="23">
+        <v>32171162</v>
+      </c>
+      <c r="E143" s="24">
+        <v>31481</v>
+      </c>
+      <c r="F143" s="22" t="s">
+        <v>1351</v>
+      </c>
+      <c r="G143" s="22" t="s">
+        <v>1352</v>
+      </c>
+      <c r="H143" s="23">
+        <v>3382449622</v>
+      </c>
+      <c r="I143" s="22" t="s">
+        <v>58</v>
+      </c>
+      <c r="J143" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K143" s="22" t="s">
+        <v>1353</v>
+      </c>
+      <c r="L143" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="M143" s="22" t="s">
+        <v>1354</v>
+      </c>
+      <c r="N143" s="22" t="s">
+        <v>1355</v>
+      </c>
+      <c r="O143" s="25">
+        <v>38869</v>
+      </c>
+      <c r="P143" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q143" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="R143" s="23">
+        <v>48</v>
+      </c>
+      <c r="S143" s="23">
+        <v>42</v>
+      </c>
+      <c r="T143" s="26"/>
+      <c r="U143" s="26"/>
+      <c r="V143" s="26"/>
+      <c r="W143" s="26"/>
+      <c r="X143" s="26"/>
+      <c r="Y143" s="26"/>
+      <c r="Z143" s="26"/>
+      <c r="AA143" s="26"/>
+      <c r="AB143" s="26"/>
+      <c r="AC143" s="26"/>
+      <c r="AD143" s="26"/>
+      <c r="AE143" s="26"/>
+      <c r="AF143" s="26"/>
+      <c r="AG143" s="26"/>
+      <c r="AH143" s="26"/>
+      <c r="AI143" s="26"/>
+      <c r="AJ143" s="26"/>
+      <c r="AK143" s="26"/>
+      <c r="AL143" s="26"/>
+      <c r="AM143" s="26"/>
+      <c r="AN143" s="26"/>
+      <c r="AO143" s="22" t="s">
+        <v>1356</v>
+      </c>
+      <c r="AP143" s="23">
+        <v>48063712</v>
+      </c>
+      <c r="AQ143" s="22" t="s">
+        <v>1357</v>
+      </c>
+      <c r="AR143" s="23">
+        <v>16370576</v>
+      </c>
+      <c r="AS143" s="22" t="s">
+        <v>1358</v>
+      </c>
+      <c r="AT143" s="23">
+        <v>47107310</v>
+      </c>
+      <c r="AU143" s="27">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="144" spans="1:47" ht="39" thickBot="1">
+      <c r="A144" s="6">
+        <v>46276.83520833333</v>
+      </c>
+      <c r="B144" s="7" t="s">
+        <v>1359</v>
+      </c>
+      <c r="C144" s="7" t="s">
+        <v>1360</v>
+      </c>
+      <c r="D144" s="8">
+        <v>20233051</v>
+      </c>
+      <c r="E144" s="52">
+        <v>24925</v>
+      </c>
+      <c r="F144" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="G144" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H144" s="8">
+        <v>3382454234</v>
+      </c>
+      <c r="I144" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J144" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K144" s="7" t="s">
+        <v>1361</v>
+      </c>
+      <c r="L144" s="7" t="s">
+        <v>1362</v>
+      </c>
+      <c r="M144" s="7" t="s">
+        <v>1363</v>
+      </c>
+      <c r="N144" s="7" t="s">
+        <v>1128</v>
+      </c>
+      <c r="O144" s="10">
+        <v>43800</v>
+      </c>
+      <c r="P144" s="8">
+        <v>48</v>
+      </c>
+      <c r="Q144" s="8">
+        <v>7</v>
+      </c>
+      <c r="R144" s="8">
+        <v>50</v>
+      </c>
+      <c r="S144" s="8">
+        <v>38</v>
+      </c>
+      <c r="T144" s="7" t="s">
+        <v>1364</v>
+      </c>
+      <c r="U144" s="10">
+        <v>22135</v>
+      </c>
+      <c r="V144" s="8">
+        <v>14093869</v>
+      </c>
+      <c r="W144" s="7" t="s">
+        <v>1361</v>
+      </c>
+      <c r="X144" s="11"/>
+      <c r="Y144" s="11"/>
+      <c r="Z144" s="11"/>
+      <c r="AA144" s="11"/>
+      <c r="AB144" s="11"/>
+      <c r="AC144" s="11"/>
+      <c r="AD144" s="11"/>
+      <c r="AE144" s="11"/>
+      <c r="AF144" s="11"/>
+      <c r="AG144" s="11"/>
+      <c r="AH144" s="11"/>
+      <c r="AI144" s="11"/>
+      <c r="AJ144" s="11"/>
+      <c r="AK144" s="11"/>
+      <c r="AL144" s="11"/>
+      <c r="AM144" s="11"/>
+      <c r="AN144" s="11"/>
+      <c r="AO144" s="7" t="s">
+        <v>1365</v>
+      </c>
+      <c r="AP144" s="8">
+        <v>36997428</v>
+      </c>
+      <c r="AQ144" s="7" t="s">
+        <v>1366</v>
+      </c>
+      <c r="AR144" s="8">
+        <v>14093869</v>
+      </c>
+      <c r="AS144" s="11"/>
+      <c r="AT144" s="11"/>
+      <c r="AU144" s="28">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="145" spans="1:47" ht="39" thickBot="1">
+      <c r="A145" s="21">
+        <v>46276.947743055556</v>
+      </c>
+      <c r="B145" s="22" t="s">
+        <v>1367</v>
+      </c>
+      <c r="C145" s="22" t="s">
+        <v>1368</v>
+      </c>
+      <c r="D145" s="23">
+        <v>20233079</v>
+      </c>
+      <c r="E145" s="24">
+        <v>24969</v>
+      </c>
+      <c r="F145" s="22" t="s">
+        <v>1369</v>
+      </c>
+      <c r="G145" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H145" s="22" t="s">
+        <v>1370</v>
+      </c>
+      <c r="I145" s="22" t="s">
+        <v>145</v>
+      </c>
+      <c r="J145" s="22" t="s">
+        <v>59</v>
+      </c>
+      <c r="K145" s="26"/>
+      <c r="L145" s="22" t="s">
+        <v>462</v>
+      </c>
+      <c r="M145" s="22" t="s">
+        <v>1106</v>
+      </c>
+      <c r="N145" s="22" t="s">
+        <v>433</v>
+      </c>
+      <c r="O145" s="25">
+        <v>41022</v>
+      </c>
+      <c r="P145" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q145" s="22" t="s">
+        <v>304</v>
+      </c>
+      <c r="R145" s="23">
+        <v>42</v>
+      </c>
+      <c r="S145" s="23">
+        <v>38</v>
+      </c>
+      <c r="T145" s="26"/>
+      <c r="U145" s="26"/>
+      <c r="V145" s="26"/>
+      <c r="W145" s="22" t="s">
+        <v>1371</v>
+      </c>
+      <c r="X145" s="25">
+        <v>37433</v>
+      </c>
+      <c r="Y145" s="23">
+        <v>43843295</v>
+      </c>
+      <c r="Z145" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA145" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB145" s="22" t="s">
+        <v>1372</v>
+      </c>
+      <c r="AC145" s="22" t="s">
+        <v>1373</v>
+      </c>
+      <c r="AD145" s="25">
+        <v>45832</v>
+      </c>
+      <c r="AE145" s="23">
+        <v>70683586</v>
+      </c>
+      <c r="AF145" s="26"/>
+      <c r="AG145" s="26"/>
+      <c r="AH145" s="26"/>
+      <c r="AI145" s="26"/>
+      <c r="AJ145" s="26"/>
+      <c r="AK145" s="26"/>
+      <c r="AL145" s="26"/>
+      <c r="AM145" s="26"/>
+      <c r="AN145" s="26"/>
+      <c r="AO145" s="22" t="s">
+        <v>1374</v>
+      </c>
+      <c r="AP145" s="23" t="s">
+        <v>1375</v>
+      </c>
+      <c r="AQ145" s="26"/>
+      <c r="AR145" s="26"/>
+      <c r="AS145" s="26"/>
+      <c r="AT145" s="26"/>
+      <c r="AU145" s="27">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="146" spans="1:47" ht="39" thickBot="1">
+      <c r="A146" s="6">
+        <v>46277.52449074074</v>
+      </c>
+      <c r="B146" s="7" t="s">
+        <v>1376</v>
+      </c>
+      <c r="C146" s="7" t="s">
+        <v>1377</v>
+      </c>
+      <c r="D146" s="8">
+        <v>30623002</v>
+      </c>
+      <c r="E146" s="9">
+        <v>30612</v>
+      </c>
+      <c r="F146" s="7" t="s">
+        <v>1378</v>
+      </c>
+      <c r="G146" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H146" s="8">
+        <v>3382455357</v>
+      </c>
+      <c r="I146" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J146" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K146" s="7" t="s">
+        <v>1379</v>
+      </c>
+      <c r="L146" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M146" s="7" t="s">
+        <v>1380</v>
+      </c>
+      <c r="N146" s="7" t="s">
+        <v>1381</v>
+      </c>
+      <c r="O146" s="10">
+        <v>44896</v>
+      </c>
+      <c r="P146" s="8">
+        <v>38</v>
+      </c>
+      <c r="Q146" s="8">
+        <v>2</v>
+      </c>
+      <c r="R146" s="8">
+        <v>42</v>
+      </c>
+      <c r="S146" s="8">
+        <v>37</v>
+      </c>
+      <c r="T146" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="U146" s="11"/>
+      <c r="V146" s="11"/>
+      <c r="W146" s="7" t="s">
+        <v>1382</v>
+      </c>
+      <c r="X146" s="10">
+        <v>38387</v>
+      </c>
+      <c r="Y146" s="8">
+        <v>46299646</v>
+      </c>
+      <c r="Z146" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA146" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB146" s="7" t="s">
+        <v>1383</v>
+      </c>
+      <c r="AC146" s="7" t="s">
+        <v>1384</v>
+      </c>
+      <c r="AD146" s="10">
+        <v>41063</v>
+      </c>
+      <c r="AE146" s="8">
+        <v>52363247</v>
+      </c>
+      <c r="AF146" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG146" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH146" s="11"/>
+      <c r="AI146" s="11"/>
+      <c r="AJ146" s="11"/>
+      <c r="AK146" s="11"/>
+      <c r="AL146" s="11"/>
+      <c r="AM146" s="11"/>
+      <c r="AN146" s="11"/>
+      <c r="AO146" s="7" t="s">
+        <v>1385</v>
+      </c>
+      <c r="AP146" s="8">
+        <v>30623002</v>
+      </c>
+      <c r="AQ146" s="7" t="s">
+        <v>1386</v>
+      </c>
+      <c r="AR146" s="8">
+        <v>46299646</v>
+      </c>
+      <c r="AS146" s="7" t="s">
+        <v>1384</v>
+      </c>
+      <c r="AT146" s="8">
+        <v>52363247</v>
+      </c>
+      <c r="AU146" s="28">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="147" spans="1:47" ht="26.25" thickBot="1">
+      <c r="A147" s="21">
+        <v>46277.845393518517</v>
+      </c>
+      <c r="B147" s="22" t="s">
+        <v>1387</v>
+      </c>
+      <c r="C147" s="22" t="s">
+        <v>1388</v>
+      </c>
+      <c r="D147" s="23">
+        <v>25548471</v>
+      </c>
+      <c r="E147" s="22" t="s">
+        <v>1389</v>
+      </c>
+      <c r="F147" s="22" t="s">
+        <v>1390</v>
+      </c>
+      <c r="G147" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H147" s="23">
+        <v>3382413803</v>
+      </c>
+      <c r="I147" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="J147" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="K147" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="L147" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="M147" s="22" t="s">
+        <v>1391</v>
+      </c>
+      <c r="N147" s="22" t="s">
+        <v>451</v>
+      </c>
+      <c r="O147" s="25">
+        <v>43282</v>
+      </c>
+      <c r="P147" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q147" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="R147" s="23">
+        <v>38</v>
+      </c>
+      <c r="S147" s="23">
+        <v>37</v>
+      </c>
+      <c r="T147" s="22" t="s">
+        <v>1392</v>
+      </c>
+      <c r="U147" s="25">
+        <v>26500</v>
+      </c>
+      <c r="V147" s="23">
+        <v>22711694</v>
+      </c>
+      <c r="W147" s="22" t="s">
+        <v>1393</v>
+      </c>
+      <c r="X147" s="25">
+        <v>38530</v>
+      </c>
+      <c r="Y147" s="26"/>
+      <c r="Z147" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA147" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB147" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC147" s="22" t="s">
+        <v>1394</v>
+      </c>
+      <c r="AD147" s="25">
+        <v>37673</v>
+      </c>
+      <c r="AE147" s="23">
+        <v>44928718</v>
+      </c>
+      <c r="AF147" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG147" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AH147" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="AI147" s="22" t="s">
+        <v>1395</v>
+      </c>
+      <c r="AJ147" s="25">
+        <v>41485</v>
+      </c>
+      <c r="AK147" s="23">
+        <v>53269570</v>
+      </c>
+      <c r="AL147" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM147" s="26"/>
+      <c r="AN147" s="23">
+        <v>46567491</v>
+      </c>
+      <c r="AO147" s="22" t="s">
+        <v>1393</v>
+      </c>
+      <c r="AP147" s="23">
+        <v>46567491</v>
+      </c>
+      <c r="AQ147" s="22" t="s">
+        <v>1396</v>
+      </c>
+      <c r="AR147" s="23">
+        <v>44928718</v>
+      </c>
+      <c r="AS147" s="22" t="s">
+        <v>1395</v>
+      </c>
+      <c r="AT147" s="23">
+        <v>53269570</v>
+      </c>
+      <c r="AU147" s="27">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="148" spans="1:47" ht="39" thickBot="1">
+      <c r="A148" s="6">
+        <v>46277.869803240741</v>
+      </c>
+      <c r="B148" s="7" t="s">
+        <v>1397</v>
+      </c>
+      <c r="C148" s="7" t="s">
+        <v>1398</v>
+      </c>
+      <c r="D148" s="8">
+        <v>25332932</v>
+      </c>
+      <c r="E148" s="7" t="s">
+        <v>1399</v>
+      </c>
+      <c r="F148" s="7" t="s">
+        <v>1400</v>
+      </c>
+      <c r="G148" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H148" s="8">
+        <v>3382416441</v>
+      </c>
+      <c r="I148" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J148" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K148" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="L148" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M148" s="7" t="s">
+        <v>790</v>
+      </c>
+      <c r="N148" s="7" t="s">
+        <v>1128</v>
+      </c>
+      <c r="O148" s="10">
+        <v>44896</v>
+      </c>
+      <c r="P148" s="8">
+        <v>382</v>
+      </c>
+      <c r="Q148" s="8">
+        <v>2</v>
+      </c>
+      <c r="R148" s="8">
+        <v>40</v>
+      </c>
+      <c r="S148" s="8">
+        <v>37</v>
+      </c>
+      <c r="T148" s="11"/>
+      <c r="U148" s="11"/>
+      <c r="V148" s="11"/>
+      <c r="W148" s="7" t="s">
+        <v>1401</v>
+      </c>
+      <c r="X148" s="10">
+        <v>40728</v>
+      </c>
+      <c r="Y148" s="8">
+        <v>51100661</v>
+      </c>
+      <c r="Z148" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA148" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB148" s="7" t="s">
+        <v>471</v>
+      </c>
+      <c r="AC148" s="7" t="s">
+        <v>1402</v>
+      </c>
+      <c r="AD148" s="10">
+        <v>34930</v>
+      </c>
+      <c r="AE148" s="8">
+        <v>39181759</v>
+      </c>
+      <c r="AF148" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG148" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH148" s="7" t="s">
+        <v>1403</v>
+      </c>
+      <c r="AI148" s="11"/>
+      <c r="AJ148" s="11"/>
+      <c r="AK148" s="11"/>
+      <c r="AL148" s="11"/>
+      <c r="AM148" s="11"/>
+      <c r="AN148" s="11"/>
+      <c r="AO148" s="7" t="s">
+        <v>1398</v>
+      </c>
+      <c r="AP148" s="8">
+        <v>25332932</v>
+      </c>
+      <c r="AQ148" s="11"/>
+      <c r="AR148" s="11"/>
+      <c r="AS148" s="11"/>
+      <c r="AT148" s="11"/>
+      <c r="AU148" s="28">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="149" spans="1:47" ht="39" thickBot="1">
+      <c r="A149" s="21">
+        <v>46278.444386574076</v>
+      </c>
+      <c r="B149" s="22" t="s">
+        <v>1404</v>
+      </c>
+      <c r="C149" s="22" t="s">
+        <v>1405</v>
+      </c>
+      <c r="D149" s="23">
+        <v>34175507</v>
+      </c>
+      <c r="E149" s="24">
+        <v>32680</v>
+      </c>
+      <c r="F149" s="22" t="s">
+        <v>1406</v>
+      </c>
+      <c r="G149" s="22" t="s">
+        <v>30</v>
+      </c>
+      <c r="H149" s="23">
+        <v>3382419087</v>
+      </c>
+      <c r="I149" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="J149" s="22" t="s">
+        <v>32</v>
+      </c>
+      <c r="K149" s="22" t="s">
+        <v>1407</v>
+      </c>
+      <c r="L149" s="22" t="s">
+        <v>34</v>
+      </c>
+      <c r="M149" s="22" t="s">
+        <v>1408</v>
+      </c>
+      <c r="N149" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="O149" s="25">
+        <v>44896</v>
+      </c>
+      <c r="P149" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q149" s="22" t="s">
+        <v>239</v>
+      </c>
+      <c r="R149" s="23">
+        <v>48</v>
+      </c>
+      <c r="S149" s="23">
+        <v>38</v>
+      </c>
+      <c r="T149" s="22" t="s">
+        <v>1409</v>
+      </c>
+      <c r="U149" s="25">
+        <v>31950</v>
+      </c>
+      <c r="V149" s="23">
+        <v>32901130</v>
+      </c>
+      <c r="W149" s="22" t="s">
+        <v>1410</v>
+      </c>
+      <c r="X149" s="25">
+        <v>41814</v>
+      </c>
+      <c r="Y149" s="23">
+        <v>53919463</v>
+      </c>
+      <c r="Z149" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA149" s="26"/>
+      <c r="AB149" s="26"/>
+      <c r="AC149" s="22" t="s">
+        <v>1411</v>
+      </c>
+      <c r="AD149" s="25">
+        <v>44007</v>
+      </c>
+      <c r="AE149" s="23">
+        <v>58328249</v>
+      </c>
+      <c r="AF149" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG149" s="26"/>
+      <c r="AH149" s="26"/>
+      <c r="AI149" s="22" t="s">
+        <v>1412</v>
+      </c>
+      <c r="AJ149" s="25">
+        <v>44656</v>
+      </c>
+      <c r="AK149" s="23">
+        <v>59305439</v>
+      </c>
+      <c r="AL149" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM149" s="26"/>
+      <c r="AN149" s="26"/>
+      <c r="AO149" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="AP149" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="AQ149" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="AR149" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="AS149" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="AT149" s="22" t="s">
+        <v>301</v>
+      </c>
+      <c r="AU149" s="27">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="150" spans="1:47" ht="39" thickBot="1">
+      <c r="A150" s="6">
+        <v>46278.85596064815</v>
+      </c>
+      <c r="B150" s="7" t="s">
+        <v>1413</v>
+      </c>
+      <c r="C150" s="7" t="s">
+        <v>1414</v>
+      </c>
+      <c r="D150" s="8">
+        <v>29931657</v>
+      </c>
+      <c r="E150" s="9">
+        <v>30354</v>
+      </c>
+      <c r="F150" s="7" t="s">
+        <v>1415</v>
+      </c>
+      <c r="G150" s="7" t="s">
+        <v>957</v>
+      </c>
+      <c r="H150" s="7" t="s">
+        <v>1416</v>
+      </c>
+      <c r="I150" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J150" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K150" s="11"/>
+      <c r="L150" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M150" s="7" t="s">
+        <v>327</v>
+      </c>
+      <c r="N150" s="7" t="s">
+        <v>719</v>
+      </c>
+      <c r="O150" s="10">
+        <v>44896</v>
+      </c>
+      <c r="P150" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="Q150" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="R150" s="8">
+        <v>40</v>
+      </c>
+      <c r="S150" s="8">
+        <v>35</v>
+      </c>
+      <c r="T150" s="7" t="s">
+        <v>1417</v>
+      </c>
+      <c r="U150" s="10">
+        <v>27041</v>
+      </c>
+      <c r="V150" s="8">
+        <v>23558965</v>
+      </c>
+      <c r="W150" s="7" t="s">
+        <v>1418</v>
+      </c>
+      <c r="X150" s="10">
+        <v>38359</v>
+      </c>
+      <c r="Y150" s="8">
+        <v>46299642</v>
+      </c>
+      <c r="Z150" s="11"/>
+      <c r="AA150" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB150" s="11"/>
+      <c r="AC150" s="7" t="s">
+        <v>1419</v>
+      </c>
+      <c r="AD150" s="10">
+        <v>37148</v>
+      </c>
+      <c r="AE150" s="8">
+        <v>43427769</v>
+      </c>
+      <c r="AF150" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG150" s="11"/>
+      <c r="AH150" s="11"/>
+      <c r="AI150" s="7" t="s">
+        <v>1420</v>
+      </c>
+      <c r="AJ150" s="10">
+        <v>37148</v>
+      </c>
+      <c r="AK150" s="8">
+        <v>43427768</v>
+      </c>
+      <c r="AL150" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM150" s="11"/>
+      <c r="AN150" s="11"/>
+      <c r="AO150" s="7" t="s">
+        <v>1418</v>
+      </c>
+      <c r="AP150" s="8">
+        <v>46299642</v>
+      </c>
+      <c r="AQ150" s="7" t="s">
+        <v>1421</v>
+      </c>
+      <c r="AR150" s="8">
+        <v>43427768</v>
+      </c>
+      <c r="AS150" s="7" t="s">
+        <v>1419</v>
+      </c>
+      <c r="AT150" s="8">
+        <v>43427769</v>
+      </c>
+      <c r="AU150" s="28">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="151" spans="1:47" ht="26.25" thickBot="1">
+      <c r="A151" s="21">
+        <v>46278.868263888886</v>
+      </c>
+      <c r="B151" s="22" t="s">
+        <v>1422</v>
+      </c>
+      <c r="C151" s="22" t="s">
+        <v>1423</v>
+      </c>
+      <c r="D151" s="23">
+        <v>23558965</v>
+      </c>
+      <c r="E151" s="22" t="s">
+        <v>1424</v>
+      </c>
+      <c r="F151" s="22" t="s">
+        <v>1425</v>
+      </c>
+      <c r="G151" s="22" t="s">
+        <v>1426</v>
+      </c>
+      <c r="H151" s="22" t="s">
+        <v>1427</v>
+      </c>
+      <c r="I151" s="22" t="s">
+        <v>63</v>
+      </c>
+      <c r="J151" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="K151" s="26"/>
+      <c r="L151" s="22">
+        <v>0</v>
+      </c>
+      <c r="M151" s="22" t="s">
+        <v>1428</v>
+      </c>
+      <c r="N151" s="22" t="s">
+        <v>1429</v>
+      </c>
+      <c r="O151" s="25">
+        <v>45017</v>
+      </c>
+      <c r="P151" s="23">
+        <v>46</v>
+      </c>
+      <c r="Q151" s="22" t="s">
+        <v>636</v>
+      </c>
+      <c r="R151" s="23">
+        <v>48</v>
+      </c>
+      <c r="S151" s="23">
+        <v>42</v>
+      </c>
+      <c r="T151" s="22" t="s">
+        <v>1430</v>
+      </c>
+      <c r="U151" s="25">
+        <v>30354</v>
+      </c>
+      <c r="V151" s="23">
+        <v>29931657</v>
+      </c>
+      <c r="W151" s="22" t="s">
+        <v>1431</v>
+      </c>
+      <c r="X151" s="25">
+        <v>39793</v>
+      </c>
+      <c r="Y151" s="23">
+        <v>49042473</v>
+      </c>
+      <c r="Z151" s="26"/>
+      <c r="AA151" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB151" s="26"/>
+      <c r="AC151" s="26"/>
+      <c r="AD151" s="26"/>
+      <c r="AE151" s="26"/>
+      <c r="AF151" s="26"/>
+      <c r="AG151" s="26"/>
+      <c r="AH151" s="26"/>
+      <c r="AI151" s="26"/>
+      <c r="AJ151" s="26"/>
+      <c r="AK151" s="26"/>
+      <c r="AL151" s="26"/>
+      <c r="AM151" s="26"/>
+      <c r="AN151" s="26"/>
+      <c r="AO151" s="22" t="s">
+        <v>1431</v>
+      </c>
+      <c r="AP151" s="23">
+        <v>49042473</v>
+      </c>
+      <c r="AQ151" s="26"/>
+      <c r="AR151" s="26"/>
+      <c r="AS151" s="26"/>
+      <c r="AT151" s="26"/>
+      <c r="AU151" s="27">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="152" spans="1:47" ht="64.5" thickBot="1">
+      <c r="A152" s="53">
+        <v>46279.318715277775</v>
+      </c>
+      <c r="B152" s="54" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C152" s="54" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D152" s="55">
+        <v>34408780</v>
+      </c>
+      <c r="E152" s="56">
+        <v>33079</v>
+      </c>
+      <c r="F152" s="54" t="s">
+        <v>1434</v>
+      </c>
+      <c r="G152" s="54" t="s">
+        <v>942</v>
+      </c>
+      <c r="H152" s="55">
+        <v>3382412906</v>
+      </c>
+      <c r="I152" s="54" t="s">
+        <v>58</v>
+      </c>
+      <c r="J152" s="54" t="s">
+        <v>59</v>
+      </c>
+      <c r="K152" s="54" t="s">
+        <v>1435</v>
+      </c>
+      <c r="L152" s="54" t="s">
+        <v>221</v>
+      </c>
+      <c r="M152" s="54" t="s">
+        <v>906</v>
+      </c>
+      <c r="N152" s="54" t="s">
+        <v>1436</v>
+      </c>
+      <c r="O152" s="57">
+        <v>44378</v>
+      </c>
+      <c r="P152" s="54" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q152" s="54" t="s">
+        <v>49</v>
+      </c>
+      <c r="R152" s="55">
+        <v>40</v>
+      </c>
+      <c r="S152" s="55">
+        <v>36</v>
+      </c>
+      <c r="T152" s="54" t="s">
+        <v>1437</v>
+      </c>
+      <c r="U152" s="57">
+        <v>32902</v>
+      </c>
+      <c r="V152" s="55">
+        <v>34408595</v>
+      </c>
+      <c r="W152" s="54" t="s">
+        <v>1438</v>
+      </c>
+      <c r="X152" s="57">
+        <v>43762</v>
+      </c>
+      <c r="Y152" s="55">
+        <v>57460948</v>
+      </c>
+      <c r="Z152" s="54" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA152" s="54" t="s">
+        <v>230</v>
+      </c>
+      <c r="AB152" s="54" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC152" s="58"/>
+      <c r="AD152" s="58"/>
+      <c r="AE152" s="58"/>
+      <c r="AF152" s="58"/>
+      <c r="AG152" s="58"/>
+      <c r="AH152" s="58"/>
+      <c r="AI152" s="58"/>
+      <c r="AJ152" s="58"/>
+      <c r="AK152" s="58"/>
+      <c r="AL152" s="58"/>
+      <c r="AM152" s="58"/>
+      <c r="AN152" s="58"/>
+      <c r="AO152" s="54" t="s">
+        <v>1437</v>
+      </c>
+      <c r="AP152" s="55">
+        <v>34408780</v>
+      </c>
+      <c r="AQ152" s="54" t="s">
+        <v>1438</v>
+      </c>
+      <c r="AR152" s="55">
+        <v>57460948</v>
+      </c>
+      <c r="AS152" s="58"/>
+      <c r="AT152" s="58"/>
+      <c r="AU152" s="59">
+        <v>513</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/declara.xlsx
+++ b/declara.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3942" uniqueCount="1805">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4184" uniqueCount="1902">
   <si>
     <t>Marca temporal</t>
   </si>
@@ -5429,6 +5429,297 @@
   </si>
   <si>
     <t>Peña maia delfina</t>
+  </si>
+  <si>
+    <t>ponchogabo@gmail.com</t>
+  </si>
+  <si>
+    <t>Lupi Gustavo Marcelo</t>
+  </si>
+  <si>
+    <t>Santa Rosa 211</t>
+  </si>
+  <si>
+    <t>Técnico en automotores</t>
+  </si>
+  <si>
+    <t>Corralon-taller</t>
+  </si>
+  <si>
+    <t>Lupi Roldán delfina violeta</t>
+  </si>
+  <si>
+    <t>Enfermeria</t>
+  </si>
+  <si>
+    <t>estelachacon123456@gmail.com</t>
+  </si>
+  <si>
+    <t>Chacon Estela Maria</t>
+  </si>
+  <si>
+    <t>San Geronimo 165</t>
+  </si>
+  <si>
+    <t>Palacio Municipal</t>
+  </si>
+  <si>
+    <t>Lizarralde Evelyn Natali</t>
+  </si>
+  <si>
+    <t>mj7971631@gmail.com</t>
+  </si>
+  <si>
+    <t>Juárez Marcos Matías</t>
+  </si>
+  <si>
+    <t>04.01.1996</t>
+  </si>
+  <si>
+    <t>Falucho 353</t>
+  </si>
+  <si>
+    <t>Predio municipal</t>
+  </si>
+  <si>
+    <t>Alasia María Alejandra</t>
+  </si>
+  <si>
+    <t>33.363.967</t>
+  </si>
+  <si>
+    <t>Eva luna Juárez</t>
+  </si>
+  <si>
+    <t>52.363.231</t>
+  </si>
+  <si>
+    <t>Xiomara Maitén Juárez</t>
+  </si>
+  <si>
+    <t>54.341.191</t>
+  </si>
+  <si>
+    <t>maluchim9@gmail.com</t>
+  </si>
+  <si>
+    <t>Facundo Muñoz</t>
+  </si>
+  <si>
+    <t>Primitivo galán 480</t>
+  </si>
+  <si>
+    <t>Conductor</t>
+  </si>
+  <si>
+    <t>Débora obermeller</t>
+  </si>
+  <si>
+    <t>Malena Muñoz</t>
+  </si>
+  <si>
+    <t>Brito Nancy</t>
+  </si>
+  <si>
+    <t>Medrano</t>
+  </si>
+  <si>
+    <t>Bachillerato y administración contable</t>
+  </si>
+  <si>
+    <t>Albornoz Marcos Lautaro</t>
+  </si>
+  <si>
+    <t>Bruno Imanol Morales</t>
+  </si>
+  <si>
+    <t>magelesq@gmail.com</t>
+  </si>
+  <si>
+    <t>Quinteros María de los Angeles</t>
+  </si>
+  <si>
+    <t>Catamarca 295</t>
+  </si>
+  <si>
+    <t>Lic en Trabajo Social</t>
+  </si>
+  <si>
+    <t>Trabajadora Social</t>
+  </si>
+  <si>
+    <t>Marcos Alfredo Beroiz</t>
+  </si>
+  <si>
+    <t>Beroiz Quinteros Agustina</t>
+  </si>
+  <si>
+    <t>Mariano Beroiz Quinteros</t>
+  </si>
+  <si>
+    <t>Josefina Beroiz Quinteros</t>
+  </si>
+  <si>
+    <t>raul5cordoba@gmail.com</t>
+  </si>
+  <si>
+    <t>Raúl Andrés cordoba</t>
+  </si>
+  <si>
+    <t>Brown 1150</t>
+  </si>
+  <si>
+    <t>Raúl Andrés Cordoba</t>
+  </si>
+  <si>
+    <t>18/10/1891</t>
+  </si>
+  <si>
+    <t>Juana Rosa Ortiz</t>
+  </si>
+  <si>
+    <t>robertoluisrivero8@gmail.com</t>
+  </si>
+  <si>
+    <t>rivero roberto luis</t>
+  </si>
+  <si>
+    <t>falucho 340</t>
+  </si>
+  <si>
+    <t>primario</t>
+  </si>
+  <si>
+    <t>espasio verde</t>
+  </si>
+  <si>
+    <t>monica rafaela acuña</t>
+  </si>
+  <si>
+    <t>rivero ian yutiel</t>
+  </si>
+  <si>
+    <t>5 año</t>
+  </si>
+  <si>
+    <t>rocio aylen acuña rivero</t>
+  </si>
+  <si>
+    <t>3 año</t>
+  </si>
+  <si>
+    <t>milagros noelia rivero</t>
+  </si>
+  <si>
+    <t>ian yutiel rivero</t>
+  </si>
+  <si>
+    <t>cale69308@gmail.com</t>
+  </si>
+  <si>
+    <t>Carlos Ale</t>
+  </si>
+  <si>
+    <t>Las Heras 260</t>
+  </si>
+  <si>
+    <t>Prinario</t>
+  </si>
+  <si>
+    <t>Corralón Municipal</t>
+  </si>
+  <si>
+    <t>Tareas varias</t>
+  </si>
+  <si>
+    <t>Carla Sofía Ale</t>
+  </si>
+  <si>
+    <t>lauragaggini15@gmail.com</t>
+  </si>
+  <si>
+    <t>Gaggini laura</t>
+  </si>
+  <si>
+    <t>Julián sosa 227</t>
+  </si>
+  <si>
+    <t>Hipertensión tiroides</t>
+  </si>
+  <si>
+    <t>Gaggini lauranoelia</t>
+  </si>
+  <si>
+    <t>Bruno Amadeo gaggini</t>
+  </si>
+  <si>
+    <t>Laura Noelia gaggini</t>
+  </si>
+  <si>
+    <t>Gaggini laura noelia</t>
+  </si>
+  <si>
+    <t>gerotesssio@gmail.com</t>
+  </si>
+  <si>
+    <t>Bracco leandro ivan</t>
+  </si>
+  <si>
+    <t>Previo</t>
+  </si>
+  <si>
+    <t>Bracco milton jose</t>
+  </si>
+  <si>
+    <t>San jose 2070</t>
+  </si>
+  <si>
+    <t>Bracco daiana paola</t>
+  </si>
+  <si>
+    <t>Vallejos Liliana Graciela</t>
+  </si>
+  <si>
+    <t>Tiroides y diabetes</t>
+  </si>
+  <si>
+    <t>José Luis Pérez soria</t>
+  </si>
+  <si>
+    <t>Pérez José alejandro</t>
+  </si>
+  <si>
+    <t>Pérez Soria jose luis</t>
+  </si>
+  <si>
+    <t>cristianpirulo87@gmail.com</t>
+  </si>
+  <si>
+    <t>Ludueña Cristian</t>
+  </si>
+  <si>
+    <t>Peatonal 1446</t>
+  </si>
+  <si>
+    <t>Secundario imcompleto</t>
+  </si>
+  <si>
+    <t>Modino jaquiline</t>
+  </si>
+  <si>
+    <t>Ludueña Agata Michele</t>
+  </si>
+  <si>
+    <t>Estudiando el secundario</t>
+  </si>
+  <si>
+    <t>Ludueña Atahualpa Oreste Jesus</t>
+  </si>
+  <si>
+    <t>Cursando la primaria</t>
+  </si>
+  <si>
+    <t>Modino jaqueline</t>
   </si>
 </sst>
 </file>
@@ -5486,7 +5777,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -5734,11 +6025,86 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -5851,6 +6217,48 @@
     </xf>
     <xf numFmtId="15" fontId="3" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="3" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="3" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="3" fillId="3" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="3" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -6146,7 +6554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AY199"/>
+  <dimension ref="A1:AY212"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.42578125" customWidth="1"/>
@@ -29485,6 +29893,1519 @@
         <v>561</v>
       </c>
     </row>
+    <row r="200" spans="1:47" ht="39" thickBot="1">
+      <c r="A200" s="39">
+        <v>46280.415324074071</v>
+      </c>
+      <c r="B200" s="40" t="s">
+        <v>1805</v>
+      </c>
+      <c r="C200" s="40" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D200" s="41">
+        <v>26346129</v>
+      </c>
+      <c r="E200" s="42">
+        <v>28469</v>
+      </c>
+      <c r="F200" s="40" t="s">
+        <v>1807</v>
+      </c>
+      <c r="G200" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="H200" s="41">
+        <v>3382412402</v>
+      </c>
+      <c r="I200" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="J200" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="K200" s="40" t="s">
+        <v>1808</v>
+      </c>
+      <c r="L200" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="M200" s="40" t="s">
+        <v>1809</v>
+      </c>
+      <c r="N200" s="40" t="s">
+        <v>682</v>
+      </c>
+      <c r="O200" s="43">
+        <v>40575</v>
+      </c>
+      <c r="P200" s="41">
+        <v>44</v>
+      </c>
+      <c r="Q200" s="41">
+        <v>44</v>
+      </c>
+      <c r="R200" s="41">
+        <v>46</v>
+      </c>
+      <c r="S200" s="41">
+        <v>40</v>
+      </c>
+      <c r="T200" s="44"/>
+      <c r="U200" s="44"/>
+      <c r="V200" s="44"/>
+      <c r="W200" s="40" t="s">
+        <v>1810</v>
+      </c>
+      <c r="X200" s="43">
+        <v>37784</v>
+      </c>
+      <c r="Y200" s="41">
+        <v>44996066</v>
+      </c>
+      <c r="Z200" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA200" s="40" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB200" s="40" t="s">
+        <v>1811</v>
+      </c>
+      <c r="AC200" s="44"/>
+      <c r="AD200" s="44"/>
+      <c r="AE200" s="44"/>
+      <c r="AF200" s="44"/>
+      <c r="AG200" s="44"/>
+      <c r="AH200" s="44"/>
+      <c r="AI200" s="44"/>
+      <c r="AJ200" s="44"/>
+      <c r="AK200" s="44"/>
+      <c r="AL200" s="44"/>
+      <c r="AM200" s="44"/>
+      <c r="AN200" s="44"/>
+      <c r="AO200" s="40" t="s">
+        <v>1810</v>
+      </c>
+      <c r="AP200" s="41">
+        <v>44996066</v>
+      </c>
+      <c r="AQ200" s="44"/>
+      <c r="AR200" s="44"/>
+      <c r="AS200" s="44"/>
+      <c r="AT200" s="44"/>
+      <c r="AU200" s="45">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="201" spans="1:47" ht="39" thickBot="1">
+      <c r="A201" s="20">
+        <v>46280.425347222219</v>
+      </c>
+      <c r="B201" s="21" t="s">
+        <v>1812</v>
+      </c>
+      <c r="C201" s="21" t="s">
+        <v>1813</v>
+      </c>
+      <c r="D201" s="22">
+        <v>16628175</v>
+      </c>
+      <c r="E201" s="23">
+        <v>23420</v>
+      </c>
+      <c r="F201" s="21" t="s">
+        <v>1814</v>
+      </c>
+      <c r="G201" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H201" s="22">
+        <v>3382465215</v>
+      </c>
+      <c r="I201" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="J201" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="K201" s="21" t="s">
+        <v>471</v>
+      </c>
+      <c r="L201" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="M201" s="21" t="s">
+        <v>451</v>
+      </c>
+      <c r="N201" s="21" t="s">
+        <v>1815</v>
+      </c>
+      <c r="O201" s="24">
+        <v>44531</v>
+      </c>
+      <c r="P201" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="Q201" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="R201" s="22">
+        <v>48</v>
+      </c>
+      <c r="S201" s="22">
+        <v>40</v>
+      </c>
+      <c r="T201" s="25"/>
+      <c r="U201" s="25"/>
+      <c r="V201" s="25"/>
+      <c r="W201" s="21" t="s">
+        <v>1816</v>
+      </c>
+      <c r="X201" s="24">
+        <v>35803</v>
+      </c>
+      <c r="Y201" s="22">
+        <v>40959491</v>
+      </c>
+      <c r="Z201" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA201" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB201" s="25"/>
+      <c r="AC201" s="25"/>
+      <c r="AD201" s="25"/>
+      <c r="AE201" s="25"/>
+      <c r="AF201" s="25"/>
+      <c r="AG201" s="25"/>
+      <c r="AH201" s="25"/>
+      <c r="AI201" s="25"/>
+      <c r="AJ201" s="25"/>
+      <c r="AK201" s="25"/>
+      <c r="AL201" s="25"/>
+      <c r="AM201" s="25"/>
+      <c r="AN201" s="25"/>
+      <c r="AO201" s="21" t="s">
+        <v>1816</v>
+      </c>
+      <c r="AP201" s="22">
+        <v>40959491</v>
+      </c>
+      <c r="AQ201" s="25"/>
+      <c r="AR201" s="25"/>
+      <c r="AS201" s="25"/>
+      <c r="AT201" s="25"/>
+      <c r="AU201" s="26">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="202" spans="1:47" ht="39" thickBot="1">
+      <c r="A202" s="6">
+        <v>46280.470949074072</v>
+      </c>
+      <c r="B202" s="7" t="s">
+        <v>1817</v>
+      </c>
+      <c r="C202" s="7" t="s">
+        <v>1818</v>
+      </c>
+      <c r="D202" s="8">
+        <v>39049350</v>
+      </c>
+      <c r="E202" s="7" t="s">
+        <v>1819</v>
+      </c>
+      <c r="F202" s="7" t="s">
+        <v>1820</v>
+      </c>
+      <c r="G202" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H202" s="8">
+        <v>3382575739</v>
+      </c>
+      <c r="I202" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="J202" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K202" s="11"/>
+      <c r="L202" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M202" s="7" t="s">
+        <v>1821</v>
+      </c>
+      <c r="N202" s="7" t="s">
+        <v>271</v>
+      </c>
+      <c r="O202" s="10">
+        <v>43800</v>
+      </c>
+      <c r="P202" s="8">
+        <v>48</v>
+      </c>
+      <c r="Q202" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="R202" s="8">
+        <v>48</v>
+      </c>
+      <c r="S202" s="8">
+        <v>42</v>
+      </c>
+      <c r="T202" s="7" t="s">
+        <v>1822</v>
+      </c>
+      <c r="U202" s="10">
+        <v>32287</v>
+      </c>
+      <c r="V202" s="8" t="s">
+        <v>1823</v>
+      </c>
+      <c r="W202" s="7" t="s">
+        <v>1824</v>
+      </c>
+      <c r="X202" s="10">
+        <v>41039</v>
+      </c>
+      <c r="Y202" s="8" t="s">
+        <v>1825</v>
+      </c>
+      <c r="Z202" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA202" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB202" s="11"/>
+      <c r="AC202" s="7" t="s">
+        <v>1826</v>
+      </c>
+      <c r="AD202" s="10">
+        <v>42019</v>
+      </c>
+      <c r="AE202" s="8" t="s">
+        <v>1827</v>
+      </c>
+      <c r="AF202" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG202" s="11"/>
+      <c r="AH202" s="11"/>
+      <c r="AI202" s="11"/>
+      <c r="AJ202" s="11"/>
+      <c r="AK202" s="11"/>
+      <c r="AL202" s="11"/>
+      <c r="AM202" s="11"/>
+      <c r="AN202" s="11"/>
+      <c r="AO202" s="7" t="s">
+        <v>1822</v>
+      </c>
+      <c r="AP202" s="8" t="s">
+        <v>1823</v>
+      </c>
+      <c r="AQ202" s="11"/>
+      <c r="AR202" s="11"/>
+      <c r="AS202" s="11"/>
+      <c r="AT202" s="11"/>
+      <c r="AU202" s="27">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="203" spans="1:47" ht="39" thickBot="1">
+      <c r="A203" s="20">
+        <v>46280.471041666664</v>
+      </c>
+      <c r="B203" s="21" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C203" s="21" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D203" s="22">
+        <v>36997369</v>
+      </c>
+      <c r="E203" s="23">
+        <v>33968</v>
+      </c>
+      <c r="F203" s="21" t="s">
+        <v>1830</v>
+      </c>
+      <c r="G203" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H203" s="22">
+        <v>3382574837</v>
+      </c>
+      <c r="I203" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="J203" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="K203" s="21" t="s">
+        <v>723</v>
+      </c>
+      <c r="L203" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="M203" s="21" t="s">
+        <v>1821</v>
+      </c>
+      <c r="N203" s="21" t="s">
+        <v>1831</v>
+      </c>
+      <c r="O203" s="24">
+        <v>40544</v>
+      </c>
+      <c r="P203" s="22">
+        <v>56</v>
+      </c>
+      <c r="Q203" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="R203" s="22">
+        <v>56</v>
+      </c>
+      <c r="S203" s="22">
+        <v>45</v>
+      </c>
+      <c r="T203" s="21" t="s">
+        <v>1832</v>
+      </c>
+      <c r="U203" s="24">
+        <v>31631</v>
+      </c>
+      <c r="V203" s="22">
+        <v>32901128</v>
+      </c>
+      <c r="W203" s="21" t="s">
+        <v>1833</v>
+      </c>
+      <c r="X203" s="24">
+        <v>41489</v>
+      </c>
+      <c r="Y203" s="22">
+        <v>53269563</v>
+      </c>
+      <c r="Z203" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA203" s="25"/>
+      <c r="AB203" s="25"/>
+      <c r="AC203" s="25"/>
+      <c r="AD203" s="25"/>
+      <c r="AE203" s="25"/>
+      <c r="AF203" s="25"/>
+      <c r="AG203" s="25"/>
+      <c r="AH203" s="25"/>
+      <c r="AI203" s="25"/>
+      <c r="AJ203" s="25"/>
+      <c r="AK203" s="25"/>
+      <c r="AL203" s="25"/>
+      <c r="AM203" s="25"/>
+      <c r="AN203" s="25"/>
+      <c r="AO203" s="21" t="s">
+        <v>1833</v>
+      </c>
+      <c r="AP203" s="22">
+        <v>53269563</v>
+      </c>
+      <c r="AQ203" s="25"/>
+      <c r="AR203" s="25"/>
+      <c r="AS203" s="25"/>
+      <c r="AT203" s="25"/>
+      <c r="AU203" s="26">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="204" spans="1:47" ht="51.75" thickBot="1">
+      <c r="A204" s="6">
+        <v>46280.477743055555</v>
+      </c>
+      <c r="B204" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C204" s="7" t="s">
+        <v>1834</v>
+      </c>
+      <c r="D204" s="8">
+        <v>32901203</v>
+      </c>
+      <c r="E204" s="9">
+        <v>32026</v>
+      </c>
+      <c r="F204" s="7" t="s">
+        <v>1835</v>
+      </c>
+      <c r="G204" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H204" s="8">
+        <v>3382454450</v>
+      </c>
+      <c r="I204" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J204" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="K204" s="7" t="s">
+        <v>1836</v>
+      </c>
+      <c r="L204" s="7" t="s">
+        <v>425</v>
+      </c>
+      <c r="M204" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="N204" s="7" t="s">
+        <v>1585</v>
+      </c>
+      <c r="O204" s="10">
+        <v>44896</v>
+      </c>
+      <c r="P204" s="8">
+        <v>44</v>
+      </c>
+      <c r="Q204" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="R204" s="8">
+        <v>46</v>
+      </c>
+      <c r="S204" s="8">
+        <v>41</v>
+      </c>
+      <c r="T204" s="11"/>
+      <c r="U204" s="11"/>
+      <c r="V204" s="11"/>
+      <c r="W204" s="7" t="s">
+        <v>253</v>
+      </c>
+      <c r="X204" s="10">
+        <v>38154</v>
+      </c>
+      <c r="Y204" s="8">
+        <v>45827758</v>
+      </c>
+      <c r="Z204" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA204" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AB204" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC204" s="7" t="s">
+        <v>1837</v>
+      </c>
+      <c r="AD204" s="10">
+        <v>39064</v>
+      </c>
+      <c r="AE204" s="8">
+        <v>47508176</v>
+      </c>
+      <c r="AF204" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG204" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AH204" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AI204" s="7" t="s">
+        <v>255</v>
+      </c>
+      <c r="AJ204" s="10">
+        <v>41149</v>
+      </c>
+      <c r="AK204" s="8">
+        <v>52633630</v>
+      </c>
+      <c r="AL204" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM204" s="11"/>
+      <c r="AN204" s="11"/>
+      <c r="AO204" s="7" t="s">
+        <v>1838</v>
+      </c>
+      <c r="AP204" s="8">
+        <v>45827758</v>
+      </c>
+      <c r="AQ204" s="7" t="s">
+        <v>254</v>
+      </c>
+      <c r="AR204" s="8">
+        <v>47508176</v>
+      </c>
+      <c r="AS204" s="11"/>
+      <c r="AT204" s="11"/>
+      <c r="AU204" s="27">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="205" spans="1:47" ht="39" thickBot="1">
+      <c r="A205" s="20">
+        <v>46280.484918981485</v>
+      </c>
+      <c r="B205" s="21" t="s">
+        <v>1839</v>
+      </c>
+      <c r="C205" s="21" t="s">
+        <v>1840</v>
+      </c>
+      <c r="D205" s="22">
+        <v>28582616</v>
+      </c>
+      <c r="E205" s="22">
+        <v>240881</v>
+      </c>
+      <c r="F205" s="21" t="s">
+        <v>1841</v>
+      </c>
+      <c r="G205" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H205" s="22">
+        <v>3382414232</v>
+      </c>
+      <c r="I205" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J205" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="K205" s="21" t="s">
+        <v>1842</v>
+      </c>
+      <c r="L205" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="M205" s="21" t="s">
+        <v>1103</v>
+      </c>
+      <c r="N205" s="21" t="s">
+        <v>1843</v>
+      </c>
+      <c r="O205" s="24">
+        <v>39167</v>
+      </c>
+      <c r="P205" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q205" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="R205" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="S205" s="22">
+        <v>38</v>
+      </c>
+      <c r="T205" s="21" t="s">
+        <v>1844</v>
+      </c>
+      <c r="U205" s="24">
+        <v>29690</v>
+      </c>
+      <c r="V205" s="22">
+        <v>28572911</v>
+      </c>
+      <c r="W205" s="21" t="s">
+        <v>1845</v>
+      </c>
+      <c r="X205" s="24">
+        <v>41262</v>
+      </c>
+      <c r="Y205" s="22">
+        <v>52562800</v>
+      </c>
+      <c r="Z205" s="25"/>
+      <c r="AA205" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB205" s="25"/>
+      <c r="AC205" s="21" t="s">
+        <v>1846</v>
+      </c>
+      <c r="AD205" s="24">
+        <v>42479</v>
+      </c>
+      <c r="AE205" s="22">
+        <v>55403767</v>
+      </c>
+      <c r="AF205" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG205" s="25"/>
+      <c r="AH205" s="25"/>
+      <c r="AI205" s="21" t="s">
+        <v>1847</v>
+      </c>
+      <c r="AJ205" s="24">
+        <v>44295</v>
+      </c>
+      <c r="AK205" s="22">
+        <v>58745053</v>
+      </c>
+      <c r="AL205" s="25"/>
+      <c r="AM205" s="25"/>
+      <c r="AN205" s="25"/>
+      <c r="AO205" s="21" t="s">
+        <v>1844</v>
+      </c>
+      <c r="AP205" s="22">
+        <v>28572911</v>
+      </c>
+      <c r="AQ205" s="25"/>
+      <c r="AR205" s="25"/>
+      <c r="AS205" s="25"/>
+      <c r="AT205" s="25"/>
+      <c r="AU205" s="26">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="206" spans="1:47" ht="26.25" thickBot="1">
+      <c r="A206" s="6">
+        <v>46280.493842592594</v>
+      </c>
+      <c r="B206" s="7" t="s">
+        <v>1848</v>
+      </c>
+      <c r="C206" s="7" t="s">
+        <v>1849</v>
+      </c>
+      <c r="D206" s="8">
+        <v>36421333</v>
+      </c>
+      <c r="E206" s="8">
+        <v>18101991</v>
+      </c>
+      <c r="F206" s="7" t="s">
+        <v>1850</v>
+      </c>
+      <c r="G206" s="7" t="s">
+        <v>954</v>
+      </c>
+      <c r="H206" s="8">
+        <v>3382455284</v>
+      </c>
+      <c r="I206" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J206" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K206" s="11"/>
+      <c r="L206" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="M206" s="7" t="s">
+        <v>386</v>
+      </c>
+      <c r="N206" s="7" t="s">
+        <v>706</v>
+      </c>
+      <c r="O206" s="10">
+        <v>45505</v>
+      </c>
+      <c r="P206" s="8">
+        <v>4</v>
+      </c>
+      <c r="Q206" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="R206" s="8">
+        <v>44</v>
+      </c>
+      <c r="S206" s="8">
+        <v>40</v>
+      </c>
+      <c r="T206" s="7" t="s">
+        <v>1851</v>
+      </c>
+      <c r="U206" s="8" t="s">
+        <v>1852</v>
+      </c>
+      <c r="V206" s="8">
+        <v>36421333</v>
+      </c>
+      <c r="W206" s="11"/>
+      <c r="X206" s="11"/>
+      <c r="Y206" s="11"/>
+      <c r="Z206" s="11"/>
+      <c r="AA206" s="11"/>
+      <c r="AB206" s="11"/>
+      <c r="AC206" s="11"/>
+      <c r="AD206" s="11"/>
+      <c r="AE206" s="11"/>
+      <c r="AF206" s="11"/>
+      <c r="AG206" s="11"/>
+      <c r="AH206" s="11"/>
+      <c r="AI206" s="11"/>
+      <c r="AJ206" s="11"/>
+      <c r="AK206" s="11"/>
+      <c r="AL206" s="11"/>
+      <c r="AM206" s="11"/>
+      <c r="AN206" s="11"/>
+      <c r="AO206" s="7" t="s">
+        <v>1853</v>
+      </c>
+      <c r="AP206" s="8">
+        <v>14261968</v>
+      </c>
+      <c r="AQ206" s="11"/>
+      <c r="AR206" s="11"/>
+      <c r="AS206" s="11"/>
+      <c r="AT206" s="11"/>
+      <c r="AU206" s="27">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="207" spans="1:47" ht="39" thickBot="1">
+      <c r="A207" s="20">
+        <v>46280.506481481483</v>
+      </c>
+      <c r="B207" s="21" t="s">
+        <v>1854</v>
+      </c>
+      <c r="C207" s="21" t="s">
+        <v>1855</v>
+      </c>
+      <c r="D207" s="22">
+        <v>26318829</v>
+      </c>
+      <c r="E207" s="23">
+        <v>28441</v>
+      </c>
+      <c r="F207" s="21" t="s">
+        <v>1856</v>
+      </c>
+      <c r="G207" s="21" t="s">
+        <v>954</v>
+      </c>
+      <c r="H207" s="22">
+        <v>3382449264</v>
+      </c>
+      <c r="I207" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J207" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="K207" s="21" t="s">
+        <v>1857</v>
+      </c>
+      <c r="L207" s="21" t="s">
+        <v>592</v>
+      </c>
+      <c r="M207" s="21" t="s">
+        <v>1858</v>
+      </c>
+      <c r="N207" s="21" t="s">
+        <v>1858</v>
+      </c>
+      <c r="O207" s="24">
+        <v>43800</v>
+      </c>
+      <c r="P207" s="22">
+        <v>42</v>
+      </c>
+      <c r="Q207" s="22">
+        <v>42</v>
+      </c>
+      <c r="R207" s="22">
+        <v>48</v>
+      </c>
+      <c r="S207" s="22">
+        <v>41</v>
+      </c>
+      <c r="T207" s="21" t="s">
+        <v>1859</v>
+      </c>
+      <c r="U207" s="24">
+        <v>31387</v>
+      </c>
+      <c r="V207" s="22">
+        <v>31887782</v>
+      </c>
+      <c r="W207" s="21" t="s">
+        <v>1860</v>
+      </c>
+      <c r="X207" s="24">
+        <v>42647</v>
+      </c>
+      <c r="Y207" s="22">
+        <v>55798277</v>
+      </c>
+      <c r="Z207" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA207" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="AB207" s="21" t="s">
+        <v>1861</v>
+      </c>
+      <c r="AC207" s="21" t="s">
+        <v>1862</v>
+      </c>
+      <c r="AD207" s="24">
+        <v>38615</v>
+      </c>
+      <c r="AE207" s="22">
+        <v>46654541</v>
+      </c>
+      <c r="AF207" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG207" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="AH207" s="21" t="s">
+        <v>1863</v>
+      </c>
+      <c r="AI207" s="21" t="s">
+        <v>1864</v>
+      </c>
+      <c r="AJ207" s="24">
+        <v>39436</v>
+      </c>
+      <c r="AK207" s="22">
+        <v>47779588</v>
+      </c>
+      <c r="AL207" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="AM207" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="AN207" s="21" t="s">
+        <v>1744</v>
+      </c>
+      <c r="AO207" s="21" t="s">
+        <v>1862</v>
+      </c>
+      <c r="AP207" s="22">
+        <v>46654541</v>
+      </c>
+      <c r="AQ207" s="21" t="s">
+        <v>1864</v>
+      </c>
+      <c r="AR207" s="22">
+        <v>47779588</v>
+      </c>
+      <c r="AS207" s="21" t="s">
+        <v>1865</v>
+      </c>
+      <c r="AT207" s="22">
+        <v>55798277</v>
+      </c>
+      <c r="AU207" s="26">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="208" spans="1:47" ht="26.25" thickBot="1">
+      <c r="A208" s="6">
+        <v>46280.535949074074</v>
+      </c>
+      <c r="B208" s="7" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C208" s="7" t="s">
+        <v>1867</v>
+      </c>
+      <c r="D208" s="8">
+        <v>39049347</v>
+      </c>
+      <c r="E208" s="9">
+        <v>35094</v>
+      </c>
+      <c r="F208" s="7" t="s">
+        <v>1868</v>
+      </c>
+      <c r="G208" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H208" s="8">
+        <v>3382445428</v>
+      </c>
+      <c r="I208" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J208" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K208" s="7" t="s">
+        <v>1869</v>
+      </c>
+      <c r="L208" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="M208" s="7" t="s">
+        <v>1870</v>
+      </c>
+      <c r="N208" s="7" t="s">
+        <v>1871</v>
+      </c>
+      <c r="O208" s="10">
+        <v>43800</v>
+      </c>
+      <c r="P208" s="8">
+        <v>40</v>
+      </c>
+      <c r="Q208" s="8">
+        <v>40</v>
+      </c>
+      <c r="R208" s="8">
+        <v>42</v>
+      </c>
+      <c r="S208" s="8">
+        <v>40</v>
+      </c>
+      <c r="T208" s="7" t="s">
+        <v>1872</v>
+      </c>
+      <c r="U208" s="10">
+        <v>42845</v>
+      </c>
+      <c r="V208" s="8">
+        <v>56298122</v>
+      </c>
+      <c r="W208" s="7" t="s">
+        <v>1872</v>
+      </c>
+      <c r="X208" s="10">
+        <v>42845</v>
+      </c>
+      <c r="Y208" s="8">
+        <v>56298122</v>
+      </c>
+      <c r="Z208" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA208" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="AB208" s="11"/>
+      <c r="AC208" s="11"/>
+      <c r="AD208" s="11"/>
+      <c r="AE208" s="11"/>
+      <c r="AF208" s="11"/>
+      <c r="AG208" s="11"/>
+      <c r="AH208" s="11"/>
+      <c r="AI208" s="11"/>
+      <c r="AJ208" s="11"/>
+      <c r="AK208" s="11"/>
+      <c r="AL208" s="11"/>
+      <c r="AM208" s="11"/>
+      <c r="AN208" s="11"/>
+      <c r="AO208" s="7" t="s">
+        <v>1872</v>
+      </c>
+      <c r="AP208" s="8">
+        <v>56298122</v>
+      </c>
+      <c r="AQ208" s="11"/>
+      <c r="AR208" s="11"/>
+      <c r="AS208" s="11"/>
+      <c r="AT208" s="11"/>
+      <c r="AU208" s="27">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="209" spans="1:47" ht="39" thickBot="1">
+      <c r="A209" s="20">
+        <v>46280.542523148149</v>
+      </c>
+      <c r="B209" s="21" t="s">
+        <v>1873</v>
+      </c>
+      <c r="C209" s="21" t="s">
+        <v>1874</v>
+      </c>
+      <c r="D209" s="22">
+        <v>36470297</v>
+      </c>
+      <c r="E209" s="23">
+        <v>33246</v>
+      </c>
+      <c r="F209" s="21" t="s">
+        <v>1875</v>
+      </c>
+      <c r="G209" s="21" t="s">
+        <v>954</v>
+      </c>
+      <c r="H209" s="22">
+        <v>3382405039</v>
+      </c>
+      <c r="I209" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="J209" s="21" t="s">
+        <v>83</v>
+      </c>
+      <c r="K209" s="25"/>
+      <c r="L209" s="21" t="s">
+        <v>1876</v>
+      </c>
+      <c r="M209" s="21" t="s">
+        <v>808</v>
+      </c>
+      <c r="N209" s="21" t="s">
+        <v>451</v>
+      </c>
+      <c r="O209" s="24">
+        <v>43800</v>
+      </c>
+      <c r="P209" s="21" t="s">
+        <v>239</v>
+      </c>
+      <c r="Q209" s="22">
+        <v>8</v>
+      </c>
+      <c r="R209" s="22">
+        <v>50</v>
+      </c>
+      <c r="S209" s="22">
+        <v>38</v>
+      </c>
+      <c r="T209" s="21" t="s">
+        <v>1877</v>
+      </c>
+      <c r="U209" s="24">
+        <v>33246</v>
+      </c>
+      <c r="V209" s="22">
+        <v>35470297</v>
+      </c>
+      <c r="W209" s="21" t="s">
+        <v>1878</v>
+      </c>
+      <c r="X209" s="24">
+        <v>46260</v>
+      </c>
+      <c r="Y209" s="22">
+        <v>71254594</v>
+      </c>
+      <c r="Z209" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="AA209" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="AB209" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="AC209" s="21" t="s">
+        <v>1878</v>
+      </c>
+      <c r="AD209" s="24">
+        <v>46260</v>
+      </c>
+      <c r="AE209" s="22">
+        <v>71254594</v>
+      </c>
+      <c r="AF209" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="AG209" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="AH209" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="AI209" s="21" t="s">
+        <v>1878</v>
+      </c>
+      <c r="AJ209" s="24">
+        <v>46260</v>
+      </c>
+      <c r="AK209" s="22">
+        <v>71254594</v>
+      </c>
+      <c r="AL209" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="AM209" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="AN209" s="21" t="s">
+        <v>230</v>
+      </c>
+      <c r="AO209" s="21" t="s">
+        <v>1879</v>
+      </c>
+      <c r="AP209" s="22">
+        <v>35470297</v>
+      </c>
+      <c r="AQ209" s="21" t="s">
+        <v>1880</v>
+      </c>
+      <c r="AR209" s="22">
+        <v>35470297</v>
+      </c>
+      <c r="AS209" s="21" t="s">
+        <v>1880</v>
+      </c>
+      <c r="AT209" s="22">
+        <v>35479297</v>
+      </c>
+      <c r="AU209" s="26">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="210" spans="1:47" ht="26.25" thickBot="1">
+      <c r="A210" s="6">
+        <v>46280.576215277775</v>
+      </c>
+      <c r="B210" s="7" t="s">
+        <v>1881</v>
+      </c>
+      <c r="C210" s="7" t="s">
+        <v>1882</v>
+      </c>
+      <c r="D210" s="8">
+        <v>32171103</v>
+      </c>
+      <c r="E210" s="9">
+        <v>31420</v>
+      </c>
+      <c r="F210" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="G210" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="H210" s="8">
+        <v>3382449310</v>
+      </c>
+      <c r="I210" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="J210" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="K210" s="11"/>
+      <c r="L210" s="7" t="s">
+        <v>265</v>
+      </c>
+      <c r="M210" s="7" t="s">
+        <v>1883</v>
+      </c>
+      <c r="N210" s="7" t="s">
+        <v>706</v>
+      </c>
+      <c r="O210" s="10">
+        <v>39234</v>
+      </c>
+      <c r="P210" s="8">
+        <v>40</v>
+      </c>
+      <c r="Q210" s="8">
+        <v>2</v>
+      </c>
+      <c r="R210" s="8">
+        <v>40</v>
+      </c>
+      <c r="S210" s="8">
+        <v>39</v>
+      </c>
+      <c r="T210" s="11"/>
+      <c r="U210" s="11"/>
+      <c r="V210" s="8">
+        <v>50642564</v>
+      </c>
+      <c r="W210" s="7" t="s">
+        <v>1884</v>
+      </c>
+      <c r="X210" s="10">
+        <v>40596</v>
+      </c>
+      <c r="Y210" s="8">
+        <v>50642564</v>
+      </c>
+      <c r="Z210" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA210" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="AB210" s="7" t="s">
+        <v>1885</v>
+      </c>
+      <c r="AC210" s="11"/>
+      <c r="AD210" s="11"/>
+      <c r="AE210" s="11"/>
+      <c r="AF210" s="11"/>
+      <c r="AG210" s="11"/>
+      <c r="AH210" s="11"/>
+      <c r="AI210" s="11"/>
+      <c r="AJ210" s="11"/>
+      <c r="AK210" s="11"/>
+      <c r="AL210" s="11"/>
+      <c r="AM210" s="11"/>
+      <c r="AN210" s="11"/>
+      <c r="AO210" s="7" t="s">
+        <v>1886</v>
+      </c>
+      <c r="AP210" s="8">
+        <v>36997428</v>
+      </c>
+      <c r="AQ210" s="11"/>
+      <c r="AR210" s="11"/>
+      <c r="AS210" s="11"/>
+      <c r="AT210" s="11"/>
+      <c r="AU210" s="27">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="211" spans="1:47" ht="39" thickBot="1">
+      <c r="A211" s="20">
+        <v>46280.586030092592</v>
+      </c>
+      <c r="B211" s="21" t="s">
+        <v>1436</v>
+      </c>
+      <c r="C211" s="21" t="s">
+        <v>1887</v>
+      </c>
+      <c r="D211" s="22">
+        <v>24656372</v>
+      </c>
+      <c r="E211" s="23">
+        <v>27888</v>
+      </c>
+      <c r="F211" s="21" t="s">
+        <v>1438</v>
+      </c>
+      <c r="G211" s="21" t="s">
+        <v>30</v>
+      </c>
+      <c r="H211" s="22">
+        <v>3382454400</v>
+      </c>
+      <c r="I211" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="J211" s="21" t="s">
+        <v>59</v>
+      </c>
+      <c r="K211" s="25"/>
+      <c r="L211" s="21" t="s">
+        <v>1888</v>
+      </c>
+      <c r="M211" s="21" t="s">
+        <v>231</v>
+      </c>
+      <c r="N211" s="21" t="s">
+        <v>472</v>
+      </c>
+      <c r="O211" s="24">
+        <v>43800</v>
+      </c>
+      <c r="P211" s="22">
+        <v>50</v>
+      </c>
+      <c r="Q211" s="21" t="s">
+        <v>272</v>
+      </c>
+      <c r="R211" s="22">
+        <v>60</v>
+      </c>
+      <c r="S211" s="22">
+        <v>40</v>
+      </c>
+      <c r="T211" s="21" t="s">
+        <v>1889</v>
+      </c>
+      <c r="U211" s="24">
+        <v>26516</v>
+      </c>
+      <c r="V211" s="22">
+        <v>22797052</v>
+      </c>
+      <c r="W211" s="21" t="s">
+        <v>1890</v>
+      </c>
+      <c r="X211" s="24">
+        <v>35093</v>
+      </c>
+      <c r="Y211" s="22">
+        <v>39049374</v>
+      </c>
+      <c r="Z211" s="25"/>
+      <c r="AA211" s="25"/>
+      <c r="AB211" s="25"/>
+      <c r="AC211" s="21" t="s">
+        <v>1441</v>
+      </c>
+      <c r="AD211" s="24">
+        <v>36868</v>
+      </c>
+      <c r="AE211" s="22">
+        <v>424532512</v>
+      </c>
+      <c r="AF211" s="25"/>
+      <c r="AG211" s="25"/>
+      <c r="AH211" s="25"/>
+      <c r="AI211" s="21" t="s">
+        <v>1442</v>
+      </c>
+      <c r="AJ211" s="24">
+        <v>37533</v>
+      </c>
+      <c r="AK211" s="22">
+        <v>44067877</v>
+      </c>
+      <c r="AL211" s="25"/>
+      <c r="AM211" s="25"/>
+      <c r="AN211" s="25"/>
+      <c r="AO211" s="21" t="s">
+        <v>1891</v>
+      </c>
+      <c r="AP211" s="22">
+        <v>22797052</v>
+      </c>
+      <c r="AQ211" s="25"/>
+      <c r="AR211" s="25"/>
+      <c r="AS211" s="25"/>
+      <c r="AT211" s="25"/>
+      <c r="AU211" s="26">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="212" spans="1:47" ht="51.75" thickBot="1">
+      <c r="A212" s="46">
+        <v>46280.604131944441</v>
+      </c>
+      <c r="B212" s="47" t="s">
+        <v>1892</v>
+      </c>
+      <c r="C212" s="47" t="s">
+        <v>1893</v>
+      </c>
+      <c r="D212" s="48">
+        <v>34175530</v>
+      </c>
+      <c r="E212" s="49">
+        <v>32700</v>
+      </c>
+      <c r="F212" s="47" t="s">
+        <v>1894</v>
+      </c>
+      <c r="G212" s="47" t="s">
+        <v>954</v>
+      </c>
+      <c r="H212" s="48">
+        <v>3382574880</v>
+      </c>
+      <c r="I212" s="47" t="s">
+        <v>31</v>
+      </c>
+      <c r="J212" s="47" t="s">
+        <v>83</v>
+      </c>
+      <c r="K212" s="47" t="s">
+        <v>1895</v>
+      </c>
+      <c r="L212" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="M212" s="47" t="s">
+        <v>257</v>
+      </c>
+      <c r="N212" s="47" t="s">
+        <v>328</v>
+      </c>
+      <c r="O212" s="50">
+        <v>43282</v>
+      </c>
+      <c r="P212" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="Q212" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="R212" s="48">
+        <v>52</v>
+      </c>
+      <c r="S212" s="48">
+        <v>41</v>
+      </c>
+      <c r="T212" s="47" t="s">
+        <v>1896</v>
+      </c>
+      <c r="U212" s="50">
+        <v>34492</v>
+      </c>
+      <c r="V212" s="48">
+        <v>38199473</v>
+      </c>
+      <c r="W212" s="47" t="s">
+        <v>1897</v>
+      </c>
+      <c r="X212" s="50">
+        <v>40659</v>
+      </c>
+      <c r="Y212" s="48">
+        <v>50923432</v>
+      </c>
+      <c r="Z212" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="AA212" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="AB212" s="47" t="s">
+        <v>1898</v>
+      </c>
+      <c r="AC212" s="47" t="s">
+        <v>1899</v>
+      </c>
+      <c r="AD212" s="50">
+        <v>43285</v>
+      </c>
+      <c r="AE212" s="48">
+        <v>56298192</v>
+      </c>
+      <c r="AF212" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="AG212" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="AH212" s="47" t="s">
+        <v>1900</v>
+      </c>
+      <c r="AI212" s="51"/>
+      <c r="AJ212" s="51"/>
+      <c r="AK212" s="51"/>
+      <c r="AL212" s="51"/>
+      <c r="AM212" s="51"/>
+      <c r="AN212" s="51"/>
+      <c r="AO212" s="47" t="s">
+        <v>1901</v>
+      </c>
+      <c r="AP212" s="48">
+        <v>38199473</v>
+      </c>
+      <c r="AQ212" s="51"/>
+      <c r="AR212" s="51"/>
+      <c r="AS212" s="51"/>
+      <c r="AT212" s="51"/>
+      <c r="AU212" s="52">
+        <v>443</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
